--- a/results/filtered_features/mrmr_selected_features.xlsx
+++ b/results/filtered_features/mrmr_selected_features.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>relevance</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>redundancy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
         </is>
       </c>
     </row>
@@ -451,13 +461,19 @@
           <t>qP</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9999999997996406</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9999999997996406</v>
       </c>
     </row>
     <row r="3">
@@ -466,13 +482,19 @@
           <t>qP</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6533095279209553</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6533095279209553</v>
       </c>
     </row>
     <row r="4">
@@ -481,13 +503,19 @@
           <t>qP</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.543797482255204</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.543797482255204</v>
       </c>
     </row>
     <row r="5">
@@ -496,13 +524,19 @@
           <t>qP</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>T</t>
         </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5230173325662389</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1637772592228804</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3592400733433585</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +545,19 @@
           <t>qP</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>rX</t>
         </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2183500015352646</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2183500015352646</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +566,19 @@
           <t>qP_2</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9999999997913265</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9999999997913265</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +587,19 @@
           <t>qP_2</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6649502118487723</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6649502118487723</v>
       </c>
     </row>
     <row r="9">
@@ -556,13 +608,19 @@
           <t>qP_2</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>X</t>
         </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6201400208299954</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6201400208299954</v>
       </c>
     </row>
     <row r="10">
@@ -571,13 +629,19 @@
           <t>qP_2</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>T</t>
         </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6720774945003246</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1234058720853777</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5486716224149469</v>
       </c>
     </row>
     <row r="11">
@@ -586,13 +650,19 @@
           <t>qP_2</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>rX</t>
         </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2944318771430018</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2944318771430018</v>
       </c>
     </row>
     <row r="12">
@@ -601,13 +671,19 @@
           <t>rP</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>I</t>
         </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.99999999979558</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.99999999979558</v>
       </c>
     </row>
     <row r="13">
@@ -616,13 +692,19 @@
           <t>rP</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6225985573389184</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6225985573389184</v>
       </c>
     </row>
     <row r="14">
@@ -631,13 +713,19 @@
           <t>rP</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4894830668388478</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4894830668388478</v>
       </c>
     </row>
     <row r="15">
@@ -646,13 +734,19 @@
           <t>rP</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>T</t>
         </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5407445052934989</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1426392754378295</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3981052298556694</v>
       </c>
     </row>
     <row r="16">
@@ -661,13 +755,19 @@
           <t>rP</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>rX</t>
         </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2006665606295182</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2006665606295182</v>
       </c>
     </row>
   </sheetData>
